--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34D.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34D.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AAC95E-52D4-44EC-B51F-14ED38FC20C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -16,19 +22,19 @@
     <sheet name="Hidden_6" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_16">Hidden_1!$A$1:$A$26</definedName>
-    <definedName name="Hidden_210">Hidden_2!$A$1:$A$41</definedName>
-    <definedName name="Hidden_317">Hidden_3!$A$1:$A$32</definedName>
-    <definedName name="Hidden_423">Hidden_4!$A$1:$A$2</definedName>
-    <definedName name="Hidden_524">Hidden_5!$A$1:$A$3</definedName>
-    <definedName name="Hidden_625">Hidden_6!$A$1:$A$3</definedName>
+    <definedName name="Hidden_17">Hidden_1!$A$1:$A$26</definedName>
+    <definedName name="Hidden_211">Hidden_2!$A$1:$A$41</definedName>
+    <definedName name="Hidden_318">Hidden_3!$A$1:$A$32</definedName>
+    <definedName name="Hidden_424">Hidden_4!$A$1:$A$2</definedName>
+    <definedName name="Hidden_525">Hidden_5!$A$1:$A$3</definedName>
+    <definedName name="Hidden_626">Hidden_6!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="403">
   <si>
     <t>49100</t>
   </si>
@@ -84,6 +90,9 @@
     <t>438279</t>
   </si>
   <si>
+    <t>590406</t>
+  </si>
+  <si>
     <t>438270</t>
   </si>
   <si>
@@ -168,9 +177,6 @@
     <t>438300</t>
   </si>
   <si>
-    <t>438269</t>
-  </si>
-  <si>
     <t>438297</t>
   </si>
   <si>
@@ -192,6 +198,9 @@
     <t>Denominación del inmueble, en su caso</t>
   </si>
   <si>
+    <t>Fecha de adquisición</t>
+  </si>
+  <si>
     <t>Institución a cargo del inmueble</t>
   </si>
   <si>
@@ -270,112 +279,217 @@
     <t>Hipervínculo Sistema de información Inmobiliaria</t>
   </si>
   <si>
-    <t>Área de adscripción de la persona responsable del inmueble</t>
+    <t>Área de la persona servidora pública que funge como responsable inmobiliario</t>
   </si>
   <si>
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>663B4444949205F19CC71C379F86CBBF</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
+    <t>D9DC495FE03A028C5582CC143D36B3B2</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>01/01/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>Plantel 18 Atltzayanca</t>
+  </si>
+  <si>
+    <t>13/09/2012</t>
+  </si>
+  <si>
+    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Calle</t>
+  </si>
+  <si>
+    <t>Cobat</t>
+  </si>
+  <si>
+    <t>Sin número</t>
+  </si>
+  <si>
+    <t>s/n</t>
+  </si>
+  <si>
+    <t>Barrio</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
+    <t>Atltzayanca</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Tlaxcala</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Urbana</t>
+  </si>
+  <si>
+    <t>Histórico</t>
+  </si>
+  <si>
+    <t>Mixto</t>
+  </si>
+  <si>
+    <t>Educativo</t>
+  </si>
+  <si>
+    <t>Donación</t>
+  </si>
+  <si>
+    <t>1119.86</t>
+  </si>
+  <si>
+    <t>Escritura Pública</t>
+  </si>
+  <si>
+    <t>https://sistemas.indaabin.gob.mx/Inventario_Publico/</t>
+  </si>
+  <si>
+    <t>Departamento de Planeación</t>
+  </si>
+  <si>
+    <t>SUBDIRECCIÓN DE PLANEACIÓN Y EVALUACIÓN INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>17/07/2024</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>5049082B1865A3AFF4978A14FE01844A</t>
+  </si>
+  <si>
+    <t>Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>26/08/1988</t>
+  </si>
+  <si>
+    <t>República de Chile</t>
+  </si>
+  <si>
+    <t>Colonia</t>
+  </si>
+  <si>
+    <t>Venustiano Carranza</t>
+  </si>
+  <si>
+    <t>Xaloztoc</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Ejido</t>
+  </si>
+  <si>
+    <t>Constancia de posesión</t>
+  </si>
+  <si>
+    <t>F2E79ED7F163EE58BB366E1C4E3AE254</t>
+  </si>
+  <si>
+    <t>Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>19/11/2013</t>
+  </si>
+  <si>
+    <t>Avenida</t>
+  </si>
+  <si>
+    <t>Juan Ponce de León</t>
+  </si>
+  <si>
+    <t>San Antonio, Seccion uno</t>
+  </si>
+  <si>
+    <t>Ixtenco</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>133344.8</t>
+  </si>
+  <si>
+    <t>DF6A2E62FDBC203AC2233637D981AE2C</t>
+  </si>
+  <si>
+    <t>Plantel 21 Ayometla</t>
+  </si>
+  <si>
+    <t>01/07/2015</t>
+  </si>
+  <si>
+    <t>Ignacio Aldama</t>
+  </si>
+  <si>
+    <t>Pueblo</t>
+  </si>
+  <si>
+    <t>Santa Catarina Ayometla</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>4994952.15</t>
+  </si>
+  <si>
+    <t>7C8733923320A57302B764F1A6C15ADA</t>
   </si>
   <si>
     <t>Plantel 22 Texoloc</t>
   </si>
   <si>
-    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Calle</t>
+    <t>12/03/2013</t>
   </si>
   <si>
     <t>Monterrey</t>
   </si>
   <si>
-    <t>Sin número</t>
-  </si>
-  <si>
-    <t>s/n</t>
-  </si>
-  <si>
-    <t>Barrio</t>
-  </si>
-  <si>
     <t>San Damián Texoloc</t>
   </si>
   <si>
     <t>49</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Tlaxcala</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>Mexico</t>
-  </si>
-  <si>
-    <t>Urbana</t>
-  </si>
-  <si>
-    <t>Histórico</t>
-  </si>
-  <si>
-    <t>Mixto</t>
-  </si>
-  <si>
-    <t>Educativo</t>
-  </si>
-  <si>
-    <t>Donación</t>
-  </si>
-  <si>
     <t>11052.9</t>
   </si>
   <si>
-    <t>Escritura Pública</t>
-  </si>
-  <si>
-    <t>https://sistemas.indaabin.gob.mx/Inventario_Publico/</t>
-  </si>
-  <si>
-    <t>Departamento de Planeación</t>
-  </si>
-  <si>
-    <t>SUBDIRECCIÓN DE PLANEACIÓN Y EVALUACIÓN INSTITUCIONAL</t>
-  </si>
-  <si>
-    <t>06/07/2023</t>
-  </si>
-  <si>
-    <t>F092A75DBD0D44001E4CFF947CD01161</t>
+    <t>6030B778E9C96A357F929F7A92A0E126</t>
   </si>
   <si>
     <t>Plantel 23 San Pablo del Monte</t>
   </si>
   <si>
-    <t>Avenida</t>
+    <t>28/02/2013</t>
   </si>
   <si>
     <t>20 de Noviembre</t>
@@ -402,7 +516,7 @@
     <t>Acta de cabildo de Donación de Predio</t>
   </si>
   <si>
-    <t>BC723E3E684EDE9AE70470FA155EF276</t>
+    <t>061E969C7674A24B2B300E440F901B49</t>
   </si>
   <si>
     <t>Plantel 24 Tizatlán</t>
@@ -411,9 +525,6 @@
     <t>Ramón López Velarde</t>
   </si>
   <si>
-    <t>Pueblo</t>
-  </si>
-  <si>
     <t>San Esteban Tizatlan</t>
   </si>
   <si>
@@ -426,18 +537,18 @@
     <t>737946.3</t>
   </si>
   <si>
-    <t>EBA418369ECB121216880888AEA2F938</t>
+    <t>CBA237FE4C7D555253FB3394A57E94BB</t>
   </si>
   <si>
     <t>Dirección Administrativa</t>
   </si>
   <si>
+    <t>30/09/1992</t>
+  </si>
+  <si>
     <t>2 de Abril</t>
   </si>
   <si>
-    <t>Colonia</t>
-  </si>
-  <si>
     <t>Emiliano Zapata</t>
   </si>
   <si>
@@ -453,18 +564,18 @@
     <t>Compra-venta</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Copia de Certificado de Propiedad</t>
   </si>
   <si>
-    <t>B3A75E475A52B145680B5E04B506AE35</t>
+    <t>0657B04AB92FE5930211F9BAFBEFDB78</t>
   </si>
   <si>
     <t>Dirección General</t>
   </si>
   <si>
+    <t>01/12/2013</t>
+  </si>
+  <si>
     <t>Miguel N. Lira</t>
   </si>
   <si>
@@ -486,7 +597,7 @@
     <t>Ficha Técnica</t>
   </si>
   <si>
-    <t>1386067B0BB31F8462FFB959CC83C80F</t>
+    <t>322FC61F02B3BA9BB8F8040063C35240</t>
   </si>
   <si>
     <t>Plantel 01 Tlaxcala</t>
@@ -501,12 +612,15 @@
     <t>1008141</t>
   </si>
   <si>
-    <t>C96B3677AD759EA1A56A0F80AFD8989C</t>
+    <t>C78C86762BBB7103107B0D69B53945D8</t>
   </si>
   <si>
     <t>Plantel 02 Huamantla (El Calvario)</t>
   </si>
   <si>
+    <t>26/11/2013</t>
+  </si>
+  <si>
     <t>Francisco I. Madero</t>
   </si>
   <si>
@@ -519,7 +633,7 @@
     <t>Huamantla</t>
   </si>
   <si>
-    <t>C83D132E49AEAC044844063805E0DD77</t>
+    <t>CB7AD06CBC8749E3415A1733ECC3B419</t>
   </si>
   <si>
     <t>Plantel 02 Huamantla</t>
@@ -534,7 +648,7 @@
     <t>2154416</t>
   </si>
   <si>
-    <t>A4E78BA7D27E6AD15BEBBF94E2713C46</t>
+    <t>D6F1881D1533D15B86613D0EBDD35127</t>
   </si>
   <si>
     <t>Plantel 03 Calpulalpan</t>
@@ -555,12 +669,15 @@
     <t>4812303</t>
   </si>
   <si>
-    <t>7EFF0A942D065ED7ED1CB28419D101A3</t>
+    <t>CBC15E210B77D6999259ADC67F7AA3BF</t>
   </si>
   <si>
     <t>Plantel 04 Chiautempan</t>
   </si>
   <si>
+    <t>08/12/1995</t>
+  </si>
+  <si>
     <t>Campeche</t>
   </si>
   <si>
@@ -576,7 +693,7 @@
     <t>Chiautempan</t>
   </si>
   <si>
-    <t>3C6CB34514B002040A21CB9B378952DD</t>
+    <t>F37C4BFF686385D807D126A2060C0750</t>
   </si>
   <si>
     <t>Plantel 05 Panzacola</t>
@@ -603,12 +720,15 @@
     <t>17164.5</t>
   </si>
   <si>
-    <t>29C0A4257193F534F461B7BE479DC908</t>
+    <t>D3A436C031897E3AE2E0119595328A1F</t>
   </si>
   <si>
     <t>Plantel 06 Contla</t>
   </si>
   <si>
+    <t>22/03/1982</t>
+  </si>
+  <si>
     <t>20 de Mayo</t>
   </si>
   <si>
@@ -627,12 +747,15 @@
     <t>Contla de Juan Cuamatzi</t>
   </si>
   <si>
-    <t>44D0965C6F9D2F27733905B5F6465910</t>
+    <t>A1E42F4465E83AEFC07366A7E18AEFBD</t>
   </si>
   <si>
     <t>Plantel 07 Buenavista</t>
   </si>
   <si>
+    <t>15/04/2011</t>
+  </si>
+  <si>
     <t>José María Morelos</t>
   </si>
   <si>
@@ -651,21 +774,18 @@
     <t>Rústica</t>
   </si>
   <si>
-    <t>Ejido</t>
-  </si>
-  <si>
     <t>20000</t>
   </si>
   <si>
-    <t>Constancia de posesión</t>
-  </si>
-  <si>
-    <t>AC93B12A82E45610E146AE2FF1D27DFF</t>
+    <t>F328CFC39E59DD395F2B1569AD0B27CF</t>
   </si>
   <si>
     <t>Plantel 08 Ixtacuixtla</t>
   </si>
   <si>
+    <t>24/04/1983</t>
+  </si>
+  <si>
     <t>Boulevard</t>
   </si>
   <si>
@@ -681,12 +801,15 @@
     <t>Certificado de NO propiedad</t>
   </si>
   <si>
-    <t>A1C11926CB7C10BFC9199AC06839493B</t>
+    <t>2B97162CE02CFC696BF0566184037F83</t>
   </si>
   <si>
     <t>Plantel 09 Tlaxco</t>
   </si>
   <si>
+    <t>23/05/2013</t>
+  </si>
+  <si>
     <t>5 de Mayo</t>
   </si>
   <si>
@@ -696,12 +819,15 @@
     <t>50000</t>
   </si>
   <si>
-    <t>C46E12860247BF4A0BC569DC6225BE81</t>
+    <t>F08C1120B9B7926FA61D556EA756030C</t>
   </si>
   <si>
     <t>Plantel 10 Apizaco</t>
   </si>
   <si>
+    <t>28/01/2013</t>
+  </si>
+  <si>
     <t>Ricardo Ortíz García</t>
   </si>
   <si>
@@ -717,7 +843,7 @@
     <t>Apizaco</t>
   </si>
   <si>
-    <t>96912F727695DF0E7C96B26D04A06190</t>
+    <t>3A1A4F49B006F62CD4DE2696E2B9EFA4</t>
   </si>
   <si>
     <t>Plantel 11 Panotla</t>
@@ -729,12 +855,15 @@
     <t>Decreto de Expropiación</t>
   </si>
   <si>
-    <t>0696E6DE03A608235EEE2D3D5ACA9A09</t>
+    <t>35612875856958E37EEA0536FF91475A</t>
   </si>
   <si>
     <t>Plantel 12 Santa Cruz</t>
   </si>
   <si>
+    <t>30/08/2013</t>
+  </si>
+  <si>
     <t>50</t>
   </si>
   <si>
@@ -747,18 +876,24 @@
     <t>9593.4</t>
   </si>
   <si>
-    <t>746238EFFEC294D2E9C2ADC66F12B3CC</t>
+    <t>A03F36AC329FE5BDEE1F862E3A7CF3FF</t>
+  </si>
+  <si>
+    <t>21/04/1986</t>
   </si>
   <si>
     <t>10847.22</t>
   </si>
   <si>
-    <t>2E33E4E264681CB34C933E2AAD54A378</t>
+    <t>99E8280B13A740483DF4E8D23AAFB436</t>
   </si>
   <si>
     <t>Plantel 13 Papalotla</t>
   </si>
   <si>
+    <t>06/12/2013</t>
+  </si>
+  <si>
     <t>Máximo Rojas</t>
   </si>
   <si>
@@ -768,12 +903,15 @@
     <t>311654.4</t>
   </si>
   <si>
-    <t>0E64AF696A8873A7EE7C8E11C8F57159</t>
+    <t>A9A988904715A69878917227C8826737</t>
   </si>
   <si>
     <t>Plantel 14 Nativitas</t>
   </si>
   <si>
+    <t>04/09/1984</t>
+  </si>
+  <si>
     <t>Bachiller</t>
   </si>
   <si>
@@ -786,7 +924,7 @@
     <t>Certificado Parcelario Ejidal</t>
   </si>
   <si>
-    <t>E79B58768DE750843C1F1CD27DBEF14F</t>
+    <t>E83C1B465F0A8BF055FB4BD6A0F20DE0</t>
   </si>
   <si>
     <t>Plantel 15 Hueyotlipan</t>
@@ -804,7 +942,7 @@
     <t>90882.6</t>
   </si>
   <si>
-    <t>73F7959781DE6C49E49F2B00B25B50ED</t>
+    <t>F62E28DF99868BF94530D21828406AAD</t>
   </si>
   <si>
     <t>Plantel 16 Teolocholco</t>
@@ -825,7 +963,7 @@
     <t>1268208</t>
   </si>
   <si>
-    <t>83E7E46463C29F678686569587C9DD4E</t>
+    <t>915AAFC23D9142AAA28B9EB3B690A738</t>
   </si>
   <si>
     <t>Plantel 17 Cuapiaxtla</t>
@@ -841,81 +979,6 @@
   </si>
   <si>
     <t>Cuapiaxtla</t>
-  </si>
-  <si>
-    <t>E64F6D8E497A9A43EB62244C24698EAA</t>
-  </si>
-  <si>
-    <t>Plantel 18 Atltzayanca</t>
-  </si>
-  <si>
-    <t>Cobat</t>
-  </si>
-  <si>
-    <t>San Antonio</t>
-  </si>
-  <si>
-    <t>Atltzayanca</t>
-  </si>
-  <si>
-    <t>1119.86</t>
-  </si>
-  <si>
-    <t>7DAFE10EEE4912C0EE943809616306A9</t>
-  </si>
-  <si>
-    <t>Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>República de Chile</t>
-  </si>
-  <si>
-    <t>Venustiano Carranza</t>
-  </si>
-  <si>
-    <t>Xaloztoc</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>B91F7D2555A0530381105E5323CC98C2</t>
-  </si>
-  <si>
-    <t>Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>Juan Ponce de León</t>
-  </si>
-  <si>
-    <t>San Antonio, Seccion uno</t>
-  </si>
-  <si>
-    <t>Ixtenco</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>133344.8</t>
-  </si>
-  <si>
-    <t>329BFACC58F41F68AAE5A2464656DA22</t>
-  </si>
-  <si>
-    <t>Plantel 21 Ayometla</t>
-  </si>
-  <si>
-    <t>Ignacio Aldama</t>
-  </si>
-  <si>
-    <t>Santa Catarina Ayometla</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>4994952.15</t>
   </si>
   <si>
     <t>Privada</t>
@@ -1185,7 +1248,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1281,6 +1344,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -1296,44 +1362,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1361,14 +1427,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1396,6 +1479,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1407,208 +1507,184 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="48.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="50.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="45.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="59.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="61.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="62.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="55" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="38" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="57.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="51.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="50.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="62.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="55" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="38" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="57.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="20" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="8" bestFit="1" customWidth="1"/>
   </cols>
@@ -1664,49 +1740,49 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" t="s">
-        <v>6</v>
-      </c>
       <c r="J4" t="s">
         <v>6</v>
       </c>
       <c r="K4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>8</v>
       </c>
-      <c r="M4" t="s">
-        <v>6</v>
-      </c>
       <c r="N4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
         <v>8</v>
       </c>
-      <c r="O4" t="s">
-        <v>6</v>
-      </c>
       <c r="P4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" t="s">
-        <v>6</v>
-      </c>
       <c r="R4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S4" t="s">
         <v>9</v>
       </c>
-      <c r="S4" t="s">
-        <v>6</v>
-      </c>
       <c r="T4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U4" t="s">
         <v>8</v>
@@ -1718,7 +1794,7 @@
         <v>8</v>
       </c>
       <c r="X4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="s">
         <v>9</v>
@@ -1727,28 +1803,28 @@
         <v>9</v>
       </c>
       <c r="AA4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AB4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC4" t="s">
         <v>8</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>10</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>11</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>8</v>
       </c>
       <c r="AG4" t="s">
         <v>8</v>
       </c>
       <c r="AH4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="s">
         <v>12</v>
@@ -2046,19 +2122,19 @@
         <v>95</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>98</v>
@@ -2073,16 +2149,16 @@
         <v>101</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>103</v>
@@ -2115,15 +2191,15 @@
         <v>112</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>86</v>
@@ -2135,19 +2211,19 @@
         <v>88</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>94</v>
@@ -2156,22 +2232,22 @@
         <v>95</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>99</v>
@@ -2183,16 +2259,16 @@
         <v>101</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>6</v>
+        <v>121</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>103</v>
@@ -2207,13 +2283,13 @@
         <v>106</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="AF9" s="2" t="s">
         <v>110</v>
@@ -2225,15 +2301,15 @@
         <v>112</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>86</v>
@@ -2245,43 +2321,43 @@
         <v>88</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>99</v>
@@ -2293,16 +2369,16 @@
         <v>101</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="2" t="s">
         <v>103</v>
@@ -2317,10 +2393,10 @@
         <v>106</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="AE10" s="2" t="s">
         <v>109</v>
@@ -2335,15 +2411,15 @@
         <v>112</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>86</v>
@@ -2355,43 +2431,43 @@
         <v>88</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>99</v>
@@ -2403,16 +2479,16 @@
         <v>101</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y11" s="2" t="s">
         <v>103</v>
@@ -2421,16 +2497,16 @@
         <v>104</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="AC11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD11" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="AE11" s="2" t="s">
         <v>109</v>
@@ -2445,15 +2521,15 @@
         <v>112</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>86</v>
@@ -2465,43 +2541,43 @@
         <v>88</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="L12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="Q12" s="2" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>99</v>
@@ -2513,16 +2589,16 @@
         <v>101</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>103</v>
@@ -2531,16 +2607,16 @@
         <v>104</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AE12" s="2" t="s">
         <v>109</v>
@@ -2555,15 +2631,15 @@
         <v>112</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>86</v>
@@ -2575,43 +2651,43 @@
         <v>88</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="N13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="P13" s="2" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>99</v>
@@ -2623,16 +2699,16 @@
         <v>101</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y13" s="2" t="s">
         <v>103</v>
@@ -2647,13 +2723,13 @@
         <v>106</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="AD13" s="2" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="AF13" s="2" t="s">
         <v>110</v>
@@ -2665,15 +2741,15 @@
         <v>112</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>86</v>
@@ -2685,43 +2761,43 @@
         <v>88</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>93</v>
+        <v>162</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>99</v>
@@ -2733,16 +2809,16 @@
         <v>101</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>103</v>
@@ -2757,10 +2833,10 @@
         <v>106</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="AE14" s="2" t="s">
         <v>109</v>
@@ -2775,15 +2851,15 @@
         <v>112</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>86</v>
@@ -2795,43 +2871,43 @@
         <v>88</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>165</v>
+        <v>92</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>162</v>
+        <v>6</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>12</v>
+        <v>172</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>99</v>
@@ -2843,16 +2919,16 @@
         <v>101</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>6</v>
+        <v>172</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y15" s="2" t="s">
         <v>103</v>
@@ -2864,16 +2940,16 @@
         <v>105</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="AD15" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="AF15" s="2" t="s">
         <v>110</v>
@@ -2885,15 +2961,15 @@
         <v>112</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>86</v>
@@ -2905,43 +2981,43 @@
         <v>88</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>170</v>
+        <v>92</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>172</v>
+        <v>119</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>10</v>
+        <v>183</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>99</v>
@@ -2953,16 +3029,16 @@
         <v>101</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>6</v>
+        <v>183</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y16" s="2" t="s">
         <v>103</v>
@@ -2974,16 +3050,16 @@
         <v>105</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="AF16" s="2" t="s">
         <v>110</v>
@@ -2995,15 +3071,15 @@
         <v>112</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ16" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>86</v>
@@ -3015,43 +3091,43 @@
         <v>88</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>177</v>
+        <v>92</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>179</v>
+        <v>6</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>99</v>
@@ -3063,16 +3139,16 @@
         <v>101</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>6</v>
+        <v>183</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>103</v>
@@ -3084,13 +3160,13 @@
         <v>105</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="AD17" s="2" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="AE17" s="2" t="s">
         <v>109</v>
@@ -3105,15 +3181,15 @@
         <v>112</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ17" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>86</v>
@@ -3125,43 +3201,43 @@
         <v>88</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>90</v>
+        <v>194</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>184</v>
+        <v>92</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>6</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>99</v>
@@ -3173,16 +3249,16 @@
         <v>101</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>103</v>
@@ -3194,13 +3270,13 @@
         <v>105</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="AD18" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="AE18" s="2" t="s">
         <v>109</v>
@@ -3215,15 +3291,15 @@
         <v>112</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ18" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>86</v>
@@ -3235,43 +3311,43 @@
         <v>88</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>90</v>
+        <v>194</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>193</v>
+        <v>92</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>94</v>
+        <v>202</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>95</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>195</v>
+        <v>119</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>196</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q19" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>99</v>
@@ -3283,16 +3359,16 @@
         <v>101</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>196</v>
+        <v>100</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y19" s="2" t="s">
         <v>103</v>
@@ -3304,13 +3380,13 @@
         <v>105</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="AD19" s="2" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="AE19" s="2" t="s">
         <v>109</v>
@@ -3325,15 +3401,15 @@
         <v>112</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ19" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>86</v>
@@ -3345,43 +3421,43 @@
         <v>88</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>93</v>
+        <v>206</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>94</v>
+        <v>207</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>202</v>
+        <v>119</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>202</v>
+        <v>6</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>205</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>99</v>
@@ -3393,16 +3469,16 @@
         <v>101</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>202</v>
+        <v>100</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>103</v>
@@ -3414,13 +3490,13 @@
         <v>105</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="AD20" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AE20" s="2" t="s">
         <v>109</v>
@@ -3435,15 +3511,15 @@
         <v>112</v>
       </c>
       <c r="AI20" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ20" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>86</v>
@@ -3455,19 +3531,19 @@
         <v>88</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>90</v>
+        <v>213</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>212</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>213</v>
+        <v>128</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>94</v>
@@ -3476,22 +3552,22 @@
         <v>95</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>214</v>
+        <v>119</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>6</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>214</v>
+        <v>6</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>99</v>
@@ -3503,16 +3579,16 @@
         <v>101</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>6</v>
+        <v>216</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>103</v>
@@ -3524,13 +3600,13 @@
         <v>105</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="AD21" s="2" t="s">
-        <v>216</v>
+        <v>6</v>
       </c>
       <c r="AE21" s="2" t="s">
         <v>109</v>
@@ -3545,15 +3621,15 @@
         <v>112</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>86</v>
@@ -3565,43 +3641,43 @@
         <v>88</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>220</v>
+        <v>119</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>6</v>
+        <v>223</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>98</v>
+        <v>226</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>99</v>
@@ -3613,16 +3689,16 @@
         <v>101</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>6</v>
+        <v>224</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y22" s="2" t="s">
         <v>103</v>
@@ -3634,13 +3710,13 @@
         <v>105</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="AD22" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="AE22" s="2" t="s">
         <v>109</v>
@@ -3655,15 +3731,15 @@
         <v>112</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>86</v>
@@ -3675,43 +3751,43 @@
         <v>88</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>224</v>
+        <v>92</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>94</v>
+        <v>232</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>226</v>
+        <v>96</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>9</v>
+        <v>233</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>227</v>
+        <v>6</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>185</v>
+        <v>234</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>98</v>
+        <v>236</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>99</v>
@@ -3723,16 +3799,16 @@
         <v>101</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>227</v>
+        <v>100</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>6</v>
+        <v>234</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y23" s="2" t="s">
         <v>103</v>
@@ -3744,13 +3820,13 @@
         <v>105</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="AD23" s="2" t="s">
-        <v>209</v>
+        <v>114</v>
       </c>
       <c r="AE23" s="2" t="s">
         <v>109</v>
@@ -3765,15 +3841,15 @@
         <v>112</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>86</v>
@@ -3785,43 +3861,43 @@
         <v>88</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>90</v>
+        <v>239</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>231</v>
+        <v>138</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>6</v>
+        <v>241</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>137</v>
+        <v>242</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>138</v>
+        <v>241</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>98</v>
+        <v>244</v>
       </c>
       <c r="R24" s="2" t="s">
         <v>99</v>
@@ -3833,19 +3909,19 @@
         <v>101</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>6</v>
+        <v>241</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>103</v>
+        <v>245</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>104</v>
@@ -3857,13 +3933,13 @@
         <v>106</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="AD24" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AE24" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="AF24" s="2" t="s">
         <v>110</v>
@@ -3875,15 +3951,15 @@
         <v>112</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>86</v>
@@ -3895,43 +3971,43 @@
         <v>88</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>249</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>236</v>
+        <v>96</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>236</v>
+        <v>6</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>98</v>
+        <v>253</v>
       </c>
       <c r="R25" s="2" t="s">
         <v>99</v>
@@ -3943,16 +4019,16 @@
         <v>101</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>236</v>
+        <v>100</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y25" s="2" t="s">
         <v>103</v>
@@ -3967,13 +4043,13 @@
         <v>106</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>238</v>
+        <v>123</v>
       </c>
       <c r="AD25" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="AE25" s="2" t="s">
-        <v>109</v>
+        <v>254</v>
       </c>
       <c r="AF25" s="2" t="s">
         <v>110</v>
@@ -3985,15 +4061,15 @@
         <v>112</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>86</v>
@@ -4005,43 +4081,43 @@
         <v>88</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>257</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>219</v>
+        <v>92</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>236</v>
+        <v>119</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>6</v>
+        <v>259</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>236</v>
+        <v>6</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>98</v>
+        <v>244</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>99</v>
@@ -4053,16 +4129,16 @@
         <v>101</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>236</v>
+        <v>100</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>6</v>
+        <v>244</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y26" s="2" t="s">
         <v>103</v>
@@ -4077,13 +4153,13 @@
         <v>106</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
       <c r="AD26" s="2" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="AE26" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="AF26" s="2" t="s">
         <v>110</v>
@@ -4095,15 +4171,15 @@
         <v>112</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>86</v>
@@ -4115,43 +4191,43 @@
         <v>88</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>90</v>
+        <v>263</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>243</v>
+        <v>92</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>93</v>
+        <v>264</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>94</v>
+        <v>265</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>244</v>
+        <v>119</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>6</v>
+        <v>266</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>187</v>
+        <v>9</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>99</v>
@@ -4163,16 +4239,16 @@
         <v>101</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>6</v>
+        <v>267</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y27" s="2" t="s">
         <v>103</v>
@@ -4187,13 +4263,13 @@
         <v>106</v>
       </c>
       <c r="AC27" s="2" t="s">
-        <v>245</v>
+        <v>123</v>
       </c>
       <c r="AD27" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="AF27" s="2" t="s">
         <v>110</v>
@@ -4205,15 +4281,15 @@
         <v>112</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>86</v>
@@ -4225,43 +4301,43 @@
         <v>88</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>248</v>
+        <v>128</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>249</v>
+        <v>138</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>6</v>
+        <v>271</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>249</v>
+        <v>6</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>249</v>
+        <v>173</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>99</v>
@@ -4273,16 +4349,16 @@
         <v>101</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>249</v>
+        <v>100</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>6</v>
+        <v>172</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y28" s="2" t="s">
         <v>103</v>
@@ -4294,16 +4370,16 @@
         <v>105</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>251</v>
+        <v>6</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>109</v>
+        <v>272</v>
       </c>
       <c r="AF28" s="2" t="s">
         <v>110</v>
@@ -4315,15 +4391,15 @@
         <v>112</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>86</v>
@@ -4335,43 +4411,43 @@
         <v>88</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>90</v>
+        <v>275</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>254</v>
+        <v>128</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>93</v>
+        <v>258</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>94</v>
+        <v>276</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>6</v>
+        <v>277</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>256</v>
+        <v>6</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>13</v>
+        <v>277</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>98</v>
+        <v>277</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>99</v>
@@ -4383,16 +4459,16 @@
         <v>101</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>256</v>
+        <v>100</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>6</v>
+        <v>277</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>103</v>
@@ -4407,10 +4483,10 @@
         <v>106</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>257</v>
+        <v>107</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="AE29" s="2" t="s">
         <v>109</v>
@@ -4425,15 +4501,15 @@
         <v>112</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ29" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>86</v>
@@ -4445,43 +4521,43 @@
         <v>88</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>90</v>
+        <v>281</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>260</v>
+        <v>128</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>93</v>
+        <v>258</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>94</v>
+        <v>276</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>95</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>261</v>
+        <v>138</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>6</v>
+        <v>277</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>262</v>
+        <v>6</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>98</v>
+        <v>277</v>
       </c>
       <c r="R30" s="2" t="s">
         <v>99</v>
@@ -4493,16 +4569,16 @@
         <v>101</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>262</v>
+        <v>100</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>6</v>
+        <v>277</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>103</v>
@@ -4517,13 +4593,13 @@
         <v>106</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>264</v>
+        <v>107</v>
       </c>
       <c r="AD30" s="2" t="s">
-        <v>108</v>
+        <v>282</v>
       </c>
       <c r="AE30" s="2" t="s">
-        <v>109</v>
+        <v>272</v>
       </c>
       <c r="AF30" s="2" t="s">
         <v>110</v>
@@ -4535,15 +4611,15 @@
         <v>112</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>86</v>
@@ -4555,19 +4631,19 @@
         <v>88</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>90</v>
+        <v>285</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>267</v>
+        <v>91</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>268</v>
+        <v>128</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>93</v>
+        <v>286</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>94</v>
@@ -4576,22 +4652,22 @@
         <v>95</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>269</v>
+        <v>138</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>6</v>
+        <v>287</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>270</v>
+        <v>6</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>98</v>
+        <v>226</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>99</v>
@@ -4603,16 +4679,16 @@
         <v>101</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>270</v>
+        <v>100</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>6</v>
+        <v>224</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>103</v>
@@ -4627,10 +4703,10 @@
         <v>106</v>
       </c>
       <c r="AC31" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="AD31" s="2" t="s">
-        <v>108</v>
+        <v>288</v>
       </c>
       <c r="AE31" s="2" t="s">
         <v>109</v>
@@ -4645,15 +4721,15 @@
         <v>112</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>86</v>
@@ -4665,19 +4741,19 @@
         <v>88</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>90</v>
+        <v>291</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>273</v>
+        <v>128</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>93</v>
+        <v>292</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>94</v>
@@ -4686,22 +4762,22 @@
         <v>95</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>274</v>
+        <v>138</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>6</v>
+        <v>293</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>275</v>
+        <v>6</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>7</v>
+        <v>293</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>98</v>
+        <v>293</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>99</v>
@@ -4713,16 +4789,16 @@
         <v>101</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>275</v>
+        <v>100</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>6</v>
+        <v>293</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y32" s="2" t="s">
         <v>103</v>
@@ -4737,13 +4813,13 @@
         <v>106</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>276</v>
+        <v>123</v>
       </c>
       <c r="AD32" s="2" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="AE32" s="2" t="s">
-        <v>109</v>
+        <v>295</v>
       </c>
       <c r="AF32" s="2" t="s">
         <v>110</v>
@@ -4755,15 +4831,15 @@
         <v>112</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>86</v>
@@ -4775,43 +4851,43 @@
         <v>88</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>279</v>
+        <v>128</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>93</v>
+        <v>298</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>280</v>
+        <v>138</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>6</v>
+        <v>299</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>281</v>
+        <v>6</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>98</v>
+        <v>300</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>99</v>
@@ -4823,16 +4899,16 @@
         <v>101</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>281</v>
+        <v>100</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y33" s="2" t="s">
         <v>103</v>
@@ -4844,13 +4920,13 @@
         <v>105</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="AC33" s="2" t="s">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="AE33" s="2" t="s">
         <v>109</v>
@@ -4865,15 +4941,15 @@
         <v>112</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>86</v>
@@ -4885,19 +4961,19 @@
         <v>88</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>285</v>
+        <v>92</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>93</v>
+        <v>304</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>94</v>
@@ -4906,22 +4982,22 @@
         <v>95</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>286</v>
+        <v>96</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>6</v>
+        <v>305</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>287</v>
+        <v>6</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>98</v>
+        <v>306</v>
       </c>
       <c r="R34" s="2" t="s">
         <v>99</v>
@@ -4933,16 +5009,16 @@
         <v>101</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>287</v>
+        <v>100</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>6</v>
+        <v>306</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y34" s="2" t="s">
         <v>103</v>
@@ -4957,10 +5033,10 @@
         <v>106</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="AD34" s="2" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="AE34" s="2" t="s">
         <v>109</v>
@@ -4975,15 +5051,15 @@
         <v>112</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:36" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>86</v>
@@ -4995,43 +5071,43 @@
         <v>88</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>93</v>
+        <v>312</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>293</v>
+        <v>96</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>6</v>
+        <v>313</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>293</v>
+        <v>6</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>293</v>
+        <v>232</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>98</v>
+        <v>314</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>99</v>
@@ -5043,16 +5119,16 @@
         <v>101</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>293</v>
+        <v>100</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>6</v>
+        <v>314</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Y35" s="2" t="s">
         <v>103</v>
@@ -5067,10 +5143,10 @@
         <v>106</v>
       </c>
       <c r="AC35" s="2" t="s">
-        <v>295</v>
+        <v>107</v>
       </c>
       <c r="AD35" s="2" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="AE35" s="2" t="s">
         <v>109</v>
@@ -5085,10 +5161,10 @@
         <v>112</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AJ35" s="2" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -5102,23 +5178,23 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G201">
-      <formula1>Hidden_16</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H201" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>Hidden_17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K201">
-      <formula1>Hidden_210</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L201" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>Hidden_211</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R8:R201">
-      <formula1>Hidden_317</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="S8:S201" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>Hidden_318</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X201">
-      <formula1>Hidden_423</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y201" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>Hidden_424</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y201">
-      <formula1>Hidden_524</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z201" xr:uid="{00000000-0002-0000-0000-000004000000}">
+      <formula1>Hidden_525</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z201">
-      <formula1>Hidden_625</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA8:AA201" xr:uid="{00000000-0002-0000-0000-000005000000}">
+      <formula1>Hidden_626</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5126,138 +5202,138 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -5266,213 +5342,213 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -5481,168 +5557,168 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -5651,18 +5727,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -5671,23 +5747,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -5696,23 +5772,23 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34D.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34D.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AAC95E-52D4-44EC-B51F-14ED38FC20C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571B67D9-7224-468F-AB64-6F1ED92161A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
